--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630455</v>
       </c>
       <c r="B2" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128630433</v>
+        <v>128630440</v>
       </c>
       <c r="B6" t="n">
-        <v>56559</v>
+        <v>57530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1134,14 +1134,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567072</v>
+        <v>567155</v>
       </c>
       <c r="R6" t="n">
-        <v>6456837</v>
+        <v>6456747</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Den har nog sitt hemvist dvs. övernattningsplatsen i kontinuitetsskogen</t>
+          <t>Den hördes på kvällskvisten</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128630440</v>
+        <v>128630433</v>
       </c>
       <c r="B7" t="n">
-        <v>57526</v>
+        <v>56563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>205992</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1249,9 +1244,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567155</v>
+        <v>567072</v>
       </c>
       <c r="R7" t="n">
-        <v>6456747</v>
+        <v>6456837</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Den hördes på kvällskvisten</t>
+          <t>Den har nog sitt hemvist dvs. övernattningsplatsen i kontinuitetsskogen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,42 +1326,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128649062</v>
+        <v>128649081</v>
       </c>
       <c r="B8" t="n">
-        <v>98572</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567154</v>
+        <v>567137</v>
       </c>
       <c r="R8" t="n">
-        <v>6456782</v>
+        <v>6456866</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1413,7 +1413,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1432,42 +1431,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128649081</v>
+        <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>57682</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1475,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567137</v>
+        <v>567154</v>
       </c>
       <c r="R9" t="n">
-        <v>6456866</v>
+        <v>6456782</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,6 +1518,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630455</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128630440</v>
       </c>
       <c r="B6" t="n">
-        <v>57530</v>
+        <v>57557</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128630433</v>
       </c>
       <c r="B7" t="n">
-        <v>56563</v>
+        <v>56590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128649081</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630455</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128630440</v>
       </c>
       <c r="B6" t="n">
-        <v>57557</v>
+        <v>57561</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128630433</v>
       </c>
       <c r="B7" t="n">
-        <v>56590</v>
+        <v>56593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128649081</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22888-2025 artfynd.xlsx
+++ b/artfynd/A 22888-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128630455</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128649069</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>128649120</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128649084</v>
       </c>
       <c r="B5" t="n">
-        <v>91528</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128630440</v>
       </c>
       <c r="B6" t="n">
-        <v>57561</v>
+        <v>57564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128630433</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>128649081</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>128649062</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
